--- a/files/Spinney_Gantt_v2.xlsx
+++ b/files/Spinney_Gantt_v2.xlsx
@@ -1,19 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryan/Documents/GitHub/spinney/files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FFCF72-77C1-A340-BE9E-D0C4FA8C1F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="8560" yWindow="1560" windowWidth="29800" windowHeight="20420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Gantt" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Task Register" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Reference" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Gantt" sheetId="1" r:id="rId1"/>
+    <sheet name="Task Register" sheetId="2" r:id="rId2"/>
+    <sheet name="Reference" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,672 +38,692 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="218">
-  <si>
-    <t xml:space="preserve">Spinney External Works — Project Gantt (v2 — durations pending Luke's comment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last updated:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crew basis: Luke +1 (conservative). Durations are planning estimates — Luke to correct.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend: teal bar = task · gold = milestone / stage gate · grey column = Luke holiday · blue text on yellow = edit these cells (Start / End dates drive the bars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depends on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHASE 1 — SCAFFOLD &amp; AT-HEIGHT WORKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site setup &amp; garden segregation fencing (family access preserved)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke +1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaffold A + B erection (incl. discrete decking demolition at footing points)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chimney repair — cut render to substrate, realign, re-render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coping stones — cut back, lead flashing, replace stones, watertight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Back-of-house gutters — realign, lead flashing, hedgehog brushes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAGE GATE 1 — At-height works sign-off (Lara / Neels / Ryan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2–1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaffold strike (A + B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHASE 2 — GROUNDWORKS &amp; DECKING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soakaway drainage, side (a) — partial deck demo, new pipework, reposition existing pipe and realign pump as backup drainage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">queue after 1.5 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notify V4 Flooring — request decking delivery (auto: decking (a) start − 14 days)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3 start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 delivery — 6t+ Millboard &amp; substructure, PAID IN FULL 9 Jul (landing zone TBC with Luke)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 Flooring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking side (a) — strip out, new substructure, lay Millboard per design (access: gate a only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1, 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAGE GATE 2 — Decking (a) sign-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking side (b) — strip out, new substructure, lay Millboard per design (access: gate b only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G2, 3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAGE GATE 3 — Decking (b) sign-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonus — BBQ &amp; shed area from offcuts / excess, side (a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROJECT COMPLETION — snagging &amp; final sign-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHASE 3 — FLOATING / RAINY-DAY POOL (pivot here when weather or hold-ups stall the spine)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driveway channel — lift cobbles, dig waste channel, connect softener discharge to natural drainage, reinstate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front-of-house gutters and minor roof repairs— repair / realignment (ladder work)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fence spurring, side (b) — MUST complete before decking side (b) starts (latest finish: Fri 25 Sep on current plan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ before 2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree / bush clearing back to fence boundary — EXTERNAL company; scope &amp; cost outside this project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External co.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fence relocation — route per TPO outcome (original line or divert around tree)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ext. trees + TPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPO appeal decision — date TBC (branch point for 3.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-working: Luke holiday w/c 27 Jul &amp; w/c 24 Aug (grey columns); UK bank holiday Mon 31 Aug (w/c 31 Aug is a 4-day week).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Assumption: soakaway pipework is NOT gated on scaffold removal — Luke to confirm footing positions don't obstruct pipe runs at erection (Wed 15 Jul). If clear, 2.1 may pull earlier subject to the one-phase-at-a-time rule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule: work proceeds only with Luke onsite; one phase at a time (whole crew). Rainy-day pool absorbs weather losses on render/roof work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 notify (M1) and delivery (2.2) dates are formulas driven by Decking (a) start — amend 2.3 Start and they re-flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke's outline (1 Jul): render, coping and roofing ~3 working weeks total — v1 durations are more conservative; await his corrections before compressing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task Register — locations, access discipline &amp; pivot flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access rule: side (a) works use gate (a) exclusively (top-left entrance, lower/green deck); side (b) works use gate (b) exclusively (bottom-right entrance). No material movement over newly laid Millboard. Orange = upper level to summer house (see Decking_plan.pdf).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workstream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather-sensitive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rainy-day eligible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes / assumptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden segregation fencing &amp; site setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden (both sides)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keeps garden usable by family through Summer — working areas fenced, not a building site.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaffolding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erect Scaffold A (chimney) + Scaffold B (coping/gutters); discrete decking demolition at footing points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roof perimeter, two locations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor's team. Fixed: Wed 15 – Thu 16 Jul. Both towers up together; remain until Gate 1 sign-off.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chimney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut render back to substrate, fix alignment, re-render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chimney (Scaffold A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaffold A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Render weather-sensitive: no rain, not too hot. Target: complete before 22 Aug — first in queue to protect this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coping stones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut back, lead flashing, replace coping stones, make watertight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate elevation (Scaffold B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaffold B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent scaffold structure from chimney.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guttering (back)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-align, lead flashing, clean &amp; tie down hedgehog brushes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Back of house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uses scaffold while up — must complete before strike.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strike Scaffold A + B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both locations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only after Gate 1 sign-off (Lara/Neels/Ryan).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drainage (soakaway)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial demolition of existing decking, new pipework off downpipes, reposition existing pipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Back garden, side (a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate (a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMPTION: not gated on scaffold removal — Luke to confirm footings don't obstruct pipe runs at erection. Queued after Phase 1 under one-phase rule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 Flooring delivery — 6t+ Millboard &amp; substructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery / landing zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBC with Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAID IN FULL 9 Jul 2026 (£32,228.99, ref V4FQ-15584). Notify V4 14 calendar days ahead (M1). Landing zone must not breach gate segregation. 25% restocking on over-ordered materials.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking (a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove existing decking &amp; substructure; install new substructure; lay Millboard per design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soakaway side (a) — green lower + share of orange upper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate (a) ONLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Begins only after scaffold removed. Entrance = top-left of green deck on plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking (b)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As 2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driveway side (b)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate (b) ONLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrance = bottom-right of green deck on plan. No crossing over side (a) new boards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking (bonus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lay offcuts / excess for new BBQ &amp; shed area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side (a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only when decking complete; uses surplus material.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driveway channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lift bricks/cobbles, dig waste channel, connect water-softener discharge to natural drainage, reinstate cobbles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front driveway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active problem — softener currently free-flooding driveway. Prime rainy-day pivot.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guttering (front)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repair / re-alignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front of house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ladder only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No scaffold dependency.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fencing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fence spurring, side (b) first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARD CONSTRAINT: side (b) spurring must complete before decking side (b) begins (2.4) — access otherwise sub-optimal. Rainy-day eligible but with a deadline.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree / bush clearing back to fence boundary — EXTERNAL company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outside project scope and budget; details and costs handled separately. Prerequisite for fence relocation (3.5) only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fence relocation — original line (TPO appeal succeeds) or divert around tree (fails)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gated on TPO decision (T1, date TBC). Both routes pre-planned.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference — contacts, rules, assumptions, sign-off log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTACTS  (fill in yellow cells — phone / email are placeholders)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXAMPLE — Jane Doe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example row — format guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07700 900123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jane.doe@example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Decision Maker &amp; Budget Holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project management support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chief builder, head of company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right-hand man</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaffold team contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking materials storage &amp; delivery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORKING RULES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Work proceeds only if Luke is onsite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• One phase at a time — whole crew on one phase; no overlap (e.g. coping stones and drainage never run concurrently).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Crew planning basis: Luke +1 (conservative). Additional hands = schedule upside, never assumed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Working days: Monday–Friday, excluding Luke's holidays and UK bank holidays.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Luke holidays: 25 Jul – 1 Aug and 22 – 29 Aug 2026. Bank holiday: Mon 31 Aug 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Stage gates signed off by Lara, Ryan and Neels before the next stage begins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Weather rule: if render/roof work is unfavourable (rain, or too hot to render), crew pivots to the rainy-day pool (Phase 3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Access discipline: side (a) via gate (a) only; side (b) via gate (b) only. No materials over new Millboard.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• V4 Flooring: notify 2 weeks (14 calendar days) before decking materials are required onsite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY ASSUMPTIONS (open — to be confirmed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• A1: Scaffold footing positions do not obstruct soakaway pipe runs — Luke to confirm at erection, Wed 15 Jul.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• A2: All durations are planning estimates pending Luke's review of this v1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• A3: Decking (a)/(b) split ≈ 2.5 weeks each within the 5-week decking ceiling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• A4: V4 landing zone to be agreed with Luke without breaching gate segregation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• A5: TPO appeal decision date unknown — fence relocation (3.5) floats until known.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAGE GATE SIGN-OFF LOG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date signed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-height works (chimney, coping, back gutters) — scaffold may strike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking side (a) complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decking side (b) complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project completion — snagging &amp; final sign-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOW TO UPDATE THIS WORKBOOK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Edit only blue-on-yellow cells: task Start/End dates (Gantt), Last updated, contact details, and the sign-off log.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Gantt bars redraw automatically from Start/End dates — never colour grid cells by hand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• V4 notify (M1) and delivery (2.2) recalculate from Decking (a) Start — do not overwrite their formulas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• To activate a floating task: give it Start/End dates and change Status from 'Floating' to 'In progress'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Status values: Not started / In progress / Complete / Blocked / Floating.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="225">
+  <si>
+    <t>Spinney External Works — Project Gantt (v2 — durations pending Luke's comment)</t>
+  </si>
+  <si>
+    <t>Last updated:</t>
+  </si>
+  <si>
+    <t>Crew basis: Luke +1 (conservative). Durations are planning estimates — Luke to correct.</t>
+  </si>
+  <si>
+    <t>Legend: teal bar = task · gold = milestone / stage gate · grey column = Luke holiday · blue text on yellow = edit these cells (Start / End dates drive the bars)</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Depends on</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>PHASE 1 — SCAFFOLD &amp; AT-HEIGHT WORKS</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>Site setup &amp; garden segregation fencing (family access preserved)</t>
+  </si>
+  <si>
+    <t>Luke +1</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Scaffold A + B erection (incl. discrete decking demolition at footing points)</t>
+  </si>
+  <si>
+    <t>Trevor</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Chimney repair — cut render to substrate, realign, re-render</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Coping stones — cut back, lead flashing, replace stones, watertight</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Back-of-house gutters — realign, lead flashing, hedgehog brushes</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>STAGE GATE 1 — At-height works sign-off (Lara / Neels / Ryan)</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>1.2–1.4</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Scaffold strike (A + B)</t>
+  </si>
+  <si>
+    <t>PHASE 2 — GROUNDWORKS &amp; DECKING</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Soakaway drainage, side (a) — partial deck demo, new pipework, reposition existing pipe and realign pump as backup drainage</t>
+  </si>
+  <si>
+    <t>queue after 1.5 *</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>Notify V4 Flooring — request decking delivery (auto: decking (a) start − 14 days)</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>2.3 start</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>V4 delivery — 6t+ Millboard &amp; substructure, PAID IN FULL 9 Jul (landing zone TBC with Luke)</t>
+  </si>
+  <si>
+    <t>V4 Flooring</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Decking side (a) — strip out, new substructure, lay Millboard per design (access: gate a only)</t>
+  </si>
+  <si>
+    <t>2.1, 2.2</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>STAGE GATE 2 — Decking (a) sign-off</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Decking side (b) — strip out, new substructure, lay Millboard per design (access: gate b only)</t>
+  </si>
+  <si>
+    <t>G2, 3.3</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>STAGE GATE 3 — Decking (b) sign-off</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Bonus — BBQ &amp; shed area from offcuts / excess, side (a)</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>PROJECT COMPLETION — snagging &amp; final sign-off</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>PHASE 3 — FLOATING / RAINY-DAY POOL (pivot here when weather or hold-ups stall the spine)</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Driveway channel — lift cobbles, dig waste channel, connect softener discharge to natural drainage, reinstate</t>
+  </si>
+  <si>
+    <t>Floating</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Front-of-house gutters and minor roof repairs— repair / realignment (ladder work)</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Fence spurring, side (b) — MUST complete before decking side (b) starts (latest finish: Fri 25 Sep on current plan)</t>
+  </si>
+  <si>
+    <t>→ before 2.4</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Tree / bush clearing back to fence boundary — EXTERNAL company; scope &amp; cost outside this project</t>
+  </si>
+  <si>
+    <t>External co.</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Fence relocation — route per TPO outcome (original line or divert around tree)</t>
+  </si>
+  <si>
+    <t>Ext. trees + TPO</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>TPO appeal decision — date TBC (branch point for 3.5)</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>Non-working: Luke holiday w/c 27 Jul &amp; w/c 24 Aug (grey columns); UK bank holiday Mon 31 Aug (w/c 31 Aug is a 4-day week).</t>
+  </si>
+  <si>
+    <t>* Assumption: soakaway pipework is NOT gated on scaffold removal — Luke to confirm footing positions don't obstruct pipe runs at erection (Wed 15 Jul). If clear, 2.1 may pull earlier subject to the one-phase-at-a-time rule.</t>
+  </si>
+  <si>
+    <t>Rule: work proceeds only with Luke onsite; one phase at a time (whole crew). Rainy-day pool absorbs weather losses on render/roof work.</t>
+  </si>
+  <si>
+    <t>V4 notify (M1) and delivery (2.2) dates are formulas driven by Decking (a) start — amend 2.3 Start and they re-flow.</t>
+  </si>
+  <si>
+    <t>Luke's outline (1 Jul): render, coping and roofing ~3 working weeks total — v1 durations are more conservative; await his corrections before compressing.</t>
+  </si>
+  <si>
+    <t>Task Register — locations, access discipline &amp; pivot flags</t>
+  </si>
+  <si>
+    <t>Access rule: side (a) works use gate (a) exclusively (top-left entrance, lower/green deck); side (b) works use gate (b) exclusively (bottom-right entrance). No material movement over newly laid Millboard. Orange = upper level to summer house (see Decking_plan.pdf).</t>
+  </si>
+  <si>
+    <t>Workstream</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Access route</t>
+  </si>
+  <si>
+    <t>Weather-sensitive</t>
+  </si>
+  <si>
+    <t>Rainy-day eligible</t>
+  </si>
+  <si>
+    <t>Est. days</t>
+  </si>
+  <si>
+    <t>Notes / assumptions</t>
+  </si>
+  <si>
+    <t>Site setup</t>
+  </si>
+  <si>
+    <t>Garden segregation fencing &amp; site setup</t>
+  </si>
+  <si>
+    <t>Garden (both sides)</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Keeps garden usable by family through Summer — working areas fenced, not a building site.</t>
+  </si>
+  <si>
+    <t>Scaffolding</t>
+  </si>
+  <si>
+    <t>Erect Scaffold A (chimney) + Scaffold B (coping/gutters); discrete decking demolition at footing points</t>
+  </si>
+  <si>
+    <t>Roof perimeter, two locations</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Trevor's team. Fixed: Wed 15 – Thu 16 Jul. Both towers up together; remain until Gate 1 sign-off.</t>
+  </si>
+  <si>
+    <t>Chimney</t>
+  </si>
+  <si>
+    <t>Cut render back to substrate, fix alignment, re-render</t>
+  </si>
+  <si>
+    <t>Chimney (Scaffold A)</t>
+  </si>
+  <si>
+    <t>Scaffold A</t>
+  </si>
+  <si>
+    <t>Render weather-sensitive: no rain, not too hot. Target: complete before 22 Aug — first in queue to protect this.</t>
+  </si>
+  <si>
+    <t>Coping stones</t>
+  </si>
+  <si>
+    <t>Cut back, lead flashing, replace coping stones, make watertight</t>
+  </si>
+  <si>
+    <t>Separate elevation (Scaffold B)</t>
+  </si>
+  <si>
+    <t>Scaffold B</t>
+  </si>
+  <si>
+    <t>Independent scaffold structure from chimney.</t>
+  </si>
+  <si>
+    <t>Guttering (back)</t>
+  </si>
+  <si>
+    <t>Re-align, lead flashing, clean &amp; tie down hedgehog brushes</t>
+  </si>
+  <si>
+    <t>Back of house</t>
+  </si>
+  <si>
+    <t>Uses scaffold while up — must complete before strike.</t>
+  </si>
+  <si>
+    <t>Strike Scaffold A + B</t>
+  </si>
+  <si>
+    <t>Both locations</t>
+  </si>
+  <si>
+    <t>Only after Gate 1 sign-off (Lara/Neels/Ryan).</t>
+  </si>
+  <si>
+    <t>Drainage (soakaway)</t>
+  </si>
+  <si>
+    <t>Partial demolition of existing decking, new pipework off downpipes, reposition existing pipe</t>
+  </si>
+  <si>
+    <t>Back garden, side (a)</t>
+  </si>
+  <si>
+    <t>Gate (a)</t>
+  </si>
+  <si>
+    <t>ASSUMPTION: not gated on scaffold removal — Luke to confirm footings don't obstruct pipe runs at erection. Queued after Phase 1 under one-phase rule.</t>
+  </si>
+  <si>
+    <t>Decking</t>
+  </si>
+  <si>
+    <t>V4 Flooring delivery — 6t+ Millboard &amp; substructure</t>
+  </si>
+  <si>
+    <t>Delivery / landing zone</t>
+  </si>
+  <si>
+    <t>TBC with Luke</t>
+  </si>
+  <si>
+    <t>PAID IN FULL 9 Jul 2026 (£32,228.99, ref V4FQ-15584). Notify V4 14 calendar days ahead (M1). Landing zone must not breach gate segregation. 25% restocking on over-ordered materials.</t>
+  </si>
+  <si>
+    <t>Decking (a)</t>
+  </si>
+  <si>
+    <t>Remove existing decking &amp; substructure; install new substructure; lay Millboard per design</t>
+  </si>
+  <si>
+    <t>Soakaway side (a) — green lower + share of orange upper</t>
+  </si>
+  <si>
+    <t>Gate (a) ONLY</t>
+  </si>
+  <si>
+    <t>Begins only after scaffold removed. Entrance = top-left of green deck on plan.</t>
+  </si>
+  <si>
+    <t>Decking (b)</t>
+  </si>
+  <si>
+    <t>As 2.3</t>
+  </si>
+  <si>
+    <t>Driveway side (b)</t>
+  </si>
+  <si>
+    <t>Gate (b) ONLY</t>
+  </si>
+  <si>
+    <t>Entrance = bottom-right of green deck on plan. No crossing over side (a) new boards.</t>
+  </si>
+  <si>
+    <t>Decking (bonus)</t>
+  </si>
+  <si>
+    <t>Lay offcuts / excess for new BBQ &amp; shed area</t>
+  </si>
+  <si>
+    <t>Side (a)</t>
+  </si>
+  <si>
+    <t>Only when decking complete; uses surplus material.</t>
+  </si>
+  <si>
+    <t>Driveway channel</t>
+  </si>
+  <si>
+    <t>Lift bricks/cobbles, dig waste channel, connect water-softener discharge to natural drainage, reinstate cobbles</t>
+  </si>
+  <si>
+    <t>Front driveway</t>
+  </si>
+  <si>
+    <t>Front</t>
+  </si>
+  <si>
+    <t>Active problem — softener currently free-flooding driveway. Prime rainy-day pivot.</t>
+  </si>
+  <si>
+    <t>Guttering (front)</t>
+  </si>
+  <si>
+    <t>Repair / re-alignment</t>
+  </si>
+  <si>
+    <t>Front of house</t>
+  </si>
+  <si>
+    <t>Ladder only</t>
+  </si>
+  <si>
+    <t>No scaffold dependency.</t>
+  </si>
+  <si>
+    <t>Fencing</t>
+  </si>
+  <si>
+    <t>Fence spurring, side (b) first</t>
+  </si>
+  <si>
+    <t>Garden boundary</t>
+  </si>
+  <si>
+    <t>Garden</t>
+  </si>
+  <si>
+    <t>HARD CONSTRAINT: side (b) spurring must complete before decking side (b) begins (2.4) — access otherwise sub-optimal. Rainy-day eligible but with a deadline.</t>
+  </si>
+  <si>
+    <t>Tree / bush clearing back to fence boundary — EXTERNAL company</t>
+  </si>
+  <si>
+    <t>Outside project scope and budget; details and costs handled separately. Prerequisite for fence relocation (3.5) only.</t>
+  </si>
+  <si>
+    <t>Fence relocation — original line (TPO appeal succeeds) or divert around tree (fails)</t>
+  </si>
+  <si>
+    <t>Gated on TPO decision (T1, date TBC). Both routes pre-planned.</t>
+  </si>
+  <si>
+    <t>Reference — contacts, rules, assumptions, sign-off log</t>
+  </si>
+  <si>
+    <t>CONTACTS  (fill in yellow cells — phone / email are placeholders)</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>EXAMPLE — Jane Doe</t>
+  </si>
+  <si>
+    <t>Example row — format guide</t>
+  </si>
+  <si>
+    <t>07700 900123</t>
+  </si>
+  <si>
+    <t>jane.doe@example.com</t>
+  </si>
+  <si>
+    <t>Lara</t>
+  </si>
+  <si>
+    <t>Key Decision Maker &amp; Budget Holder</t>
+  </si>
+  <si>
+    <t>Neels</t>
+  </si>
+  <si>
+    <t>Project management support</t>
+  </si>
+  <si>
+    <t>Project manager</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>Chief builder, head of company</t>
+  </si>
+  <si>
+    <t>Ross</t>
+  </si>
+  <si>
+    <t>Right-hand man</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>Scaffold team contact</t>
+  </si>
+  <si>
+    <t>Decking materials storage &amp; delivery</t>
+  </si>
+  <si>
+    <t>WORKING RULES</t>
+  </si>
+  <si>
+    <t>• Work proceeds only if Luke is onsite.</t>
+  </si>
+  <si>
+    <t>• One phase at a time — whole crew on one phase; no overlap (e.g. coping stones and drainage never run concurrently).</t>
+  </si>
+  <si>
+    <t>• Crew planning basis: Luke +1 (conservative). Additional hands = schedule upside, never assumed.</t>
+  </si>
+  <si>
+    <t>• Working days: Monday–Friday, excluding Luke's holidays and UK bank holidays.</t>
+  </si>
+  <si>
+    <t>• Luke holidays: 25 Jul – 1 Aug and 22 – 29 Aug 2026. Bank holiday: Mon 31 Aug 2026.</t>
+  </si>
+  <si>
+    <t>• Stage gates signed off by Lara, Ryan and Neels before the next stage begins.</t>
+  </si>
+  <si>
+    <t>• Weather rule: if render/roof work is unfavourable (rain, or too hot to render), crew pivots to the rainy-day pool (Phase 3).</t>
+  </si>
+  <si>
+    <t>• Access discipline: side (a) via gate (a) only; side (b) via gate (b) only. No materials over new Millboard.</t>
+  </si>
+  <si>
+    <t>• V4 Flooring: notify 2 weeks (14 calendar days) before decking materials are required onsite.</t>
+  </si>
+  <si>
+    <t>KEY ASSUMPTIONS (open — to be confirmed)</t>
+  </si>
+  <si>
+    <t>• A1: Scaffold footing positions do not obstruct soakaway pipe runs — Luke to confirm at erection, Wed 15 Jul.</t>
+  </si>
+  <si>
+    <t>• A2: All durations are planning estimates pending Luke's review of this v1.</t>
+  </si>
+  <si>
+    <t>• A3: Decking (a)/(b) split ≈ 2.5 weeks each within the 5-week decking ceiling.</t>
+  </si>
+  <si>
+    <t>• A4: V4 landing zone to be agreed with Luke without breaching gate segregation.</t>
+  </si>
+  <si>
+    <t>• A5: TPO appeal decision date unknown — fence relocation (3.5) floats until known.</t>
+  </si>
+  <si>
+    <t>STAGE GATE SIGN-OFF LOG</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Date signed</t>
+  </si>
+  <si>
+    <t>At-height works (chimney, coping, back gutters) — scaffold may strike</t>
+  </si>
+  <si>
+    <t>Decking side (a) complete</t>
+  </si>
+  <si>
+    <t>Decking side (b) complete</t>
+  </si>
+  <si>
+    <t>Project completion — snagging &amp; final sign-off</t>
+  </si>
+  <si>
+    <t>HOW TO UPDATE THIS WORKBOOK</t>
+  </si>
+  <si>
+    <t>• Edit only blue-on-yellow cells: task Start/End dates (Gantt), Last updated, contact details, and the sign-off log.</t>
+  </si>
+  <si>
+    <t>• Gantt bars redraw automatically from Start/End dates — never colour grid cells by hand.</t>
+  </si>
+  <si>
+    <t>• V4 notify (M1) and delivery (2.2) recalculate from Decking (a) Start — do not overwrite their formulas.</t>
+  </si>
+  <si>
+    <t>• To activate a floating task: give it Start/End dates and change Status from 'Floating' to 'In progress'.</t>
+  </si>
+  <si>
+    <t>• Status values: Not started / In progress / Complete / Blocked / Floating.</t>
+  </si>
+  <si>
+    <t>07791 528837</t>
+  </si>
+  <si>
+    <t>larakriek@gmial.com</t>
+  </si>
+  <si>
+    <t>07880 688027</t>
+  </si>
+  <si>
+    <t>neels.kriek@gmial.com</t>
+  </si>
+  <si>
+    <t>07851 601499</t>
+  </si>
+  <si>
+    <t>ryanbishop23@gmail.com</t>
+  </si>
+  <si>
+    <t>L.G Building and Roofing Ltd</t>
+  </si>
+  <si>
+    <t>01276 488099</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="dd\ mmm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,22 +732,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF0F766E"/>
       <name val="Georgia"/>
@@ -719,7 +740,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
@@ -734,7 +755,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
@@ -742,7 +763,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -750,7 +771,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -765,12 +786,31 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
-      <family val="0"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -818,14 +858,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD1D5DB"/>
       </left>
@@ -841,150 +881,88 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -999,7 +977,64 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0D9488"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0D9488"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0D9488"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0D9488"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0D9488"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1058,47 +1093,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1F2937"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1106,12 +1157,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1140,7 +1191,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1161,7 +1212,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1212,7 +1263,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1230,54 +1281,53 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC36"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="9" style="0" width="7.5"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="97" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="29" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="3">
         <v>46216</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -1302,71 +1352,71 @@
       <c r="H5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="6">
         <v>46216</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="6">
         <v>46223</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="6">
         <v>46230</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="6">
         <v>46237</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="6">
         <v>46244</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" s="6">
         <v>46251</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="6">
         <v>46258</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="6">
         <v>46265</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="6">
         <v>46272</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="6">
         <v>46279</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" s="6">
         <v>46286</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" s="6">
         <v>46293</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U5" s="6">
         <v>46300</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="V5" s="6">
         <v>46307</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="W5" s="6">
         <v>46314</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="X5" s="6">
         <v>46321</v>
       </c>
-      <c r="Y5" s="6" t="n">
+      <c r="Y5" s="6">
         <v>46328</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="Z5" s="6">
         <v>46335</v>
       </c>
-      <c r="AA5" s="6" t="n">
+      <c r="AA5" s="6">
         <v>46342</v>
       </c>
-      <c r="AB5" s="6" t="n">
+      <c r="AB5" s="6">
         <v>46349</v>
       </c>
-      <c r="AC5" s="6" t="n">
+      <c r="AC5" s="6">
         <v>46356</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
@@ -1399,7 +1449,7 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>13</v>
       </c>
@@ -1412,16 +1462,16 @@
       <c r="D7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="10">
         <v>2</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="12">
         <v>46216</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="12">
         <v>46217</v>
       </c>
       <c r="I7" s="13"/>
@@ -1446,7 +1496,7 @@
       <c r="AB7" s="13"/>
       <c r="AC7" s="13"/>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
@@ -1459,16 +1509,16 @@
       <c r="D8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="10">
         <v>2</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="12">
         <v>46218</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="12">
         <v>46219</v>
       </c>
       <c r="I8" s="13"/>
@@ -1493,7 +1543,7 @@
       <c r="AB8" s="13"/>
       <c r="AC8" s="13"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>21</v>
       </c>
@@ -1506,16 +1556,16 @@
       <c r="D9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="10">
         <v>7</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="12">
         <v>46219</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="12">
         <v>46227</v>
       </c>
       <c r="I9" s="13"/>
@@ -1540,7 +1590,7 @@
       <c r="AB9" s="13"/>
       <c r="AC9" s="13"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>23</v>
       </c>
@@ -1553,16 +1603,16 @@
       <c r="D10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="10">
         <v>10</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="12">
         <v>46237</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="12">
         <v>46248</v>
       </c>
       <c r="I10" s="13"/>
@@ -1587,7 +1637,7 @@
       <c r="AB10" s="13"/>
       <c r="AC10" s="13"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>25</v>
       </c>
@@ -1600,16 +1650,16 @@
       <c r="D11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="10">
         <v>3</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="12">
         <v>46251</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="12">
         <v>46253</v>
       </c>
       <c r="I11" s="13"/>
@@ -1634,7 +1684,7 @@
       <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
@@ -1651,10 +1701,10 @@
       <c r="F12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="12">
         <v>46254</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="12">
         <v>46254</v>
       </c>
       <c r="I12" s="13"/>
@@ -1679,7 +1729,7 @@
       <c r="AB12" s="13"/>
       <c r="AC12" s="13"/>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>31</v>
       </c>
@@ -1692,16 +1742,16 @@
       <c r="D13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="10">
         <v>1</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="12">
         <v>46255</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="12">
         <v>46255</v>
       </c>
       <c r="I13" s="13"/>
@@ -1726,7 +1776,7 @@
       <c r="AB13" s="13"/>
       <c r="AC13" s="13"/>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
@@ -1759,7 +1809,7 @@
       <c r="AB14" s="8"/>
       <c r="AC14" s="8"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>34</v>
       </c>
@@ -1772,16 +1822,16 @@
       <c r="D15" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="10">
         <v>5</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="12">
         <v>46266</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="12">
         <v>46272</v>
       </c>
       <c r="I15" s="13"/>
@@ -1806,7 +1856,7 @@
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>37</v>
       </c>
@@ -1823,12 +1873,12 @@
       <c r="F16" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="16" t="n">
-        <f aca="false">$G$18-14</f>
+      <c r="G16" s="16">
+        <f>$G$18-14</f>
         <v>46259</v>
       </c>
-      <c r="H16" s="16" t="n">
-        <f aca="false">$G$16</f>
+      <c r="H16" s="16">
+        <f>$G$16</f>
         <v>46259</v>
       </c>
       <c r="I16" s="13"/>
@@ -1853,7 +1903,7 @@
       <c r="AB16" s="13"/>
       <c r="AC16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>41</v>
       </c>
@@ -1866,18 +1916,18 @@
       <c r="D17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="10">
         <v>2</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="16" t="n">
-        <f aca="false">$G$18-5</f>
+      <c r="G17" s="16">
+        <f>$G$18-5</f>
         <v>46268</v>
       </c>
-      <c r="H17" s="16" t="n">
-        <f aca="false">$G$18-4</f>
+      <c r="H17" s="16">
+        <f>$G$18-4</f>
         <v>46269</v>
       </c>
       <c r="I17" s="13"/>
@@ -1902,7 +1952,7 @@
       <c r="AB17" s="13"/>
       <c r="AC17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>44</v>
       </c>
@@ -1915,16 +1965,16 @@
       <c r="D18" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="10">
         <v>13</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="12">
         <v>46273</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="12">
         <v>46289</v>
       </c>
       <c r="I18" s="13"/>
@@ -1949,7 +1999,7 @@
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>47</v>
       </c>
@@ -1966,10 +2016,10 @@
       <c r="F19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="12">
         <v>46290</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="12">
         <v>46290</v>
       </c>
       <c r="I19" s="13"/>
@@ -1994,7 +2044,7 @@
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
         <v>49</v>
       </c>
@@ -2007,16 +2057,16 @@
       <c r="D20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="10">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="12">
         <v>46293</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="12">
         <v>46309</v>
       </c>
       <c r="I20" s="13"/>
@@ -2041,7 +2091,7 @@
       <c r="AB20" s="13"/>
       <c r="AC20" s="13"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>52</v>
       </c>
@@ -2058,10 +2108,10 @@
       <c r="F21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="12">
         <v>46310</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="12">
         <v>46310</v>
       </c>
       <c r="I21" s="13"/>
@@ -2086,7 +2136,7 @@
       <c r="AB21" s="13"/>
       <c r="AC21" s="13"/>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>54</v>
       </c>
@@ -2099,16 +2149,16 @@
       <c r="D22" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="10">
         <v>3</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="12">
         <v>46311</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="12">
         <v>46315</v>
       </c>
       <c r="I22" s="13"/>
@@ -2133,7 +2183,7 @@
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>56</v>
       </c>
@@ -2150,10 +2200,10 @@
       <c r="F23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="12">
         <v>46318</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="H23" s="12">
         <v>46318</v>
       </c>
       <c r="I23" s="13"/>
@@ -2178,7 +2228,7 @@
       <c r="AB23" s="13"/>
       <c r="AC23" s="13"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2211,7 +2261,7 @@
       <c r="AB24" s="8"/>
       <c r="AC24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -2224,7 +2274,7 @@
       <c r="D25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="10">
         <v>4</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -2254,7 +2304,7 @@
       <c r="AB25" s="18"/>
       <c r="AC25" s="18"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
@@ -2267,7 +2317,7 @@
       <c r="D26" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="10">
         <v>2</v>
       </c>
       <c r="F26" s="10" t="s">
@@ -2297,7 +2347,7 @@
       <c r="AB26" s="18"/>
       <c r="AC26" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
@@ -2310,7 +2360,7 @@
       <c r="D27" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="10">
         <v>3</v>
       </c>
       <c r="F27" s="10" t="s">
@@ -2340,7 +2390,7 @@
       <c r="AB27" s="18"/>
       <c r="AC27" s="18"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>68</v>
       </c>
@@ -2383,7 +2433,7 @@
       <c r="AB28" s="18"/>
       <c r="AC28" s="18"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>72</v>
       </c>
@@ -2396,7 +2446,7 @@
       <c r="D29" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="10">
         <v>4</v>
       </c>
       <c r="F29" s="10" t="s">
@@ -2426,7 +2476,7 @@
       <c r="AB29" s="18"/>
       <c r="AC29" s="18"/>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>75</v>
       </c>
@@ -2469,131 +2519,123 @@
       <c r="AB30" s="18"/>
       <c r="AC30" s="18"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I7:AC11">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>AND($G7&lt;&gt;"",$H7&lt;&gt;"",$G7&lt;=I$5+6,$H7&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I12:AC12">
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>AND(ISNUMBER($G12),ISNUMBER($H12),$G12&lt;=I$5+6,$H12&gt;=I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I13:AC13">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>AND($G13&lt;&gt;"",$H13&lt;&gt;"",$G13&lt;=I$5+6,$H13&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15:AC15">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>AND($G15&lt;&gt;"",$H15&lt;&gt;"",$G15&lt;=I$5+6,$H15&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I16:AC16">
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>AND(ISNUMBER($G16),ISNUMBER($H16),$G16&lt;=I$5+6,$H16&gt;=I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I17:AC18">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>AND($G17&lt;&gt;"",$H17&lt;&gt;"",$G17&lt;=I$5+6,$H17&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I19:AC19">
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>AND(ISNUMBER($G19),ISNUMBER($H19),$G19&lt;=I$5+6,$H19&gt;=I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I20:AC20">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>AND($G20&lt;&gt;"",$H20&lt;&gt;"",$G20&lt;=I$5+6,$H20&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I21:AC21">
+    <cfRule type="expression" dxfId="3" priority="11">
+      <formula>AND(ISNUMBER($G21),ISNUMBER($H21),$G21&lt;=I$5+6,$H21&gt;=I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I22:AC22">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>AND($G22&lt;&gt;"",$H22&lt;&gt;"",$G22&lt;=I$5+6,$H22&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:AC12">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(ISNUMBER($G12),ISNUMBER($H12),$G12&lt;=I$5+6,$H12&gt;=I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16:AC16">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(ISNUMBER($G16),ISNUMBER($H16),$G16&lt;=I$5+6,$H16&gt;=I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19:AC19">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(ISNUMBER($G19),ISNUMBER($H19),$G19&lt;=I$5+6,$H19&gt;=I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21:AC21">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(ISNUMBER($G21),ISNUMBER($H21),$G21&lt;=I$5+6,$H21&gt;=I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I23:AC23">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" dxfId="1" priority="12">
       <formula>AND(ISNUMBER($G23),ISNUMBER($H23),$G23&lt;=I$5+6,$H23&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:AC30">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>AND(ISNUMBER($G30),ISNUMBER($H30),$G30&lt;=I$5+6,$H30&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="60"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -2622,7 +2664,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
@@ -2644,14 +2686,14 @@
       <c r="G5" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="10">
         <v>2</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
@@ -2673,14 +2715,14 @@
       <c r="G6" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="10">
         <v>2</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>21</v>
       </c>
@@ -2702,14 +2744,14 @@
       <c r="G7" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="10">
         <v>7</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
@@ -2731,14 +2773,14 @@
       <c r="G8" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="10">
         <v>10</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>25</v>
       </c>
@@ -2760,14 +2802,14 @@
       <c r="G9" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="10">
         <v>3</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>31</v>
       </c>
@@ -2789,14 +2831,14 @@
       <c r="G10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="10">
         <v>1</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>34</v>
       </c>
@@ -2818,14 +2860,14 @@
       <c r="G11" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="10">
         <v>5</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>41</v>
       </c>
@@ -2847,14 +2889,14 @@
       <c r="G12" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="10">
         <v>2</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>44</v>
       </c>
@@ -2876,14 +2918,14 @@
       <c r="G13" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="10">
         <v>13</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>49</v>
       </c>
@@ -2905,14 +2947,14 @@
       <c r="G14" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H14" s="10">
         <v>13</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>54</v>
       </c>
@@ -2934,14 +2976,14 @@
       <c r="G15" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="10">
         <v>3</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>60</v>
       </c>
@@ -2963,14 +3005,14 @@
       <c r="G16" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="10">
         <v>4</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>63</v>
       </c>
@@ -2992,14 +3034,14 @@
       <c r="G17" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H17" s="10">
         <v>2</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>65</v>
       </c>
@@ -3021,14 +3063,14 @@
       <c r="G18" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="10">
         <v>3</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>68</v>
       </c>
@@ -3050,14 +3092,14 @@
       <c r="G19" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" s="10">
         <v>2</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
         <v>72</v>
       </c>
@@ -3079,7 +3121,7 @@
       <c r="G20" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H20" s="10">
         <v>4</v>
       </c>
       <c r="I20" s="11" t="s">
@@ -3087,41 +3129,35 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="16"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>165</v>
       </c>
@@ -3138,7 +3174,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
         <v>170</v>
       </c>
@@ -3155,217 +3191,231 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>174</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D6" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>176</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D7" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D8" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>179</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>181</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>183</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C13" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" s="27"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="23" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="23" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="23" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="23" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="23" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="23" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="23" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="23" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="23" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="23" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>174</v>
@@ -3377,91 +3427,91 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="25" t="s">
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="25" t="s">
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="25" t="s">
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="23" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="23" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="23" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="23" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="23" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24" t="s">
-        <v>217</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <hyperlinks>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{57C6B42B-C1FF-6F45-875D-9CBF9EA5DA08}"/>
+    <hyperlink ref="E7" r:id="rId2" xr:uid="{1A9FA7E6-1882-534E-BC0A-70178EDDA1BD}"/>
+    <hyperlink ref="E8" r:id="rId3" xr:uid="{D8149E6D-6352-7F41-A04B-1E4166893763}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/files/Spinney_Gantt_v2.xlsx
+++ b/files/Spinney_Gantt_v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryan/Documents/GitHub/spinney/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FFCF72-77C1-A340-BE9E-D0C4FA8C1F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB265D92-6A9F-654F-9495-A0B03333EE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8560" yWindow="1560" windowWidth="29800" windowHeight="20420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -694,15 +694,9 @@
     <t>07791 528837</t>
   </si>
   <si>
-    <t>larakriek@gmial.com</t>
-  </si>
-  <si>
     <t>07880 688027</t>
   </si>
   <si>
-    <t>neels.kriek@gmial.com</t>
-  </si>
-  <si>
     <t>07851 601499</t>
   </si>
   <si>
@@ -713,6 +707,12 @@
   </si>
   <si>
     <t>01276 488099</t>
+  </si>
+  <si>
+    <t>larakriek@gmail.com</t>
+  </si>
+  <si>
+    <t>neels.kriek@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -3205,7 +3205,7 @@
         <v>217</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3219,10 +3219,10 @@
         <v>29</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3236,10 +3236,10 @@
         <v>29</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3250,7 +3250,7 @@
         <v>180</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
@@ -3263,7 +3263,7 @@
         <v>182</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
@@ -3276,7 +3276,7 @@
         <v>182</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="27"/>
@@ -3289,7 +3289,7 @@
         <v>182</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
@@ -3302,7 +3302,7 @@
         <v>185</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="27"/>
@@ -3318,7 +3318,7 @@
         <v>43</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E14" s="27"/>
     </row>
